--- a/artfynd/A 17513-2022 artfynd.xlsx
+++ b/artfynd/A 17513-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 17513-2022 artfynd.xlsx
+++ b/artfynd/A 17513-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,67 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>72262792</v>
+        <v>120368019</v>
       </c>
       <c r="B2" t="n">
-        <v>44328</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>201164</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sexfläckig bastardsvärmare</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Zygaena filipendulae</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rosenkällasjön södra änden, Tinnerö Eklandskap, Ög</t>
+          <t>Äbbelyckan N, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535820.3159992401</v>
+        <v>535900</v>
       </c>
       <c r="R2" t="n">
-        <v>6468544.539848128</v>
+        <v>6468466</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -762,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-07-13</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-07-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,22 +754,379 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Skogsbryn</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Monica Andersson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Monica Andersson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>112491081</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57874</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100001</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Duvhök</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Astur gentilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Rödbergsmossen, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>535850</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6468539</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Slaka</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-10-02</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-10-02</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mari Sandell</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mari Sandell</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>72262792</v>
+      </c>
+      <c r="B4" t="n">
+        <v>45042</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>201164</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Sexfläckig bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Zygaena filipendulae</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Rosenkällasjön södra änden, Tinnerö eklandskap, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>535820</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6468545</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Slaka</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2018-07-13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2018-07-13</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Viktor Eriksson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Viktor Eriksson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>132828320</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58812</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Rödbergsmossen, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>535850</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6468539</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Slaka</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mari Sandell</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mari Sandell</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17513-2022 artfynd.xlsx
+++ b/artfynd/A 17513-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120368019</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112491081</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1012,6 +1027,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72262792</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1127,8 +1147,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132828320</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>